--- a/docs/requirements/requirements.xlsx
+++ b/docs/requirements/requirements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SON\Desktop\관통프로젝트\project\docs\requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11943D19-074D-43CC-BDAC-4FD308DE1A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F16F3F-4B91-4DF7-A7A3-3402F4C3AFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6555F27F-E6EB-4F45-8CBA-89F03A0C9748}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="2" xr2:uid="{6555F27F-E6EB-4F45-8CBA-89F03A0C9748}"/>
   </bookViews>
   <sheets>
     <sheet name="기능요약" sheetId="3" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="362">
   <si>
     <t>기능명세서</t>
   </si>
@@ -467,9 +467,6 @@
     <t>챗봇은 사용자가 입력한 금융 용어를 쉬운 표현과 예시로 설명한다.</t>
   </si>
   <si>
-    <t>LLM API 사용 여부 결정</t>
-  </si>
-  <si>
     <t>FC-CHAT-003</t>
   </si>
   <si>
@@ -1042,9 +1039,6 @@
     <t>은행 위치 조회, 현재 위치 기반 지점 조회, 거리뷰</t>
   </si>
   <si>
-    <t>금융용어 설명, 금융상품 쉬운 설명</t>
-  </si>
-  <si>
     <t>내 정보, 관심 상품, 추천 이력, 진단 이력</t>
   </si>
   <si>
@@ -1138,10 +1132,24 @@
     <t>금융용어 질문 입력, 쉬운 설명 제공, 예외 응답</t>
   </si>
   <si>
-    <t>사용자는 어려운 금융 용어 또는 금융상품 관련 질문을 입력하고 챗봇을 통해 쉬운 설명과 예시를 받을 수 있다.</t>
-  </si>
-  <si>
-    <t>모든 화면 우측 하단 플로팅 버튼, LLM API 사용 여부 결정</t>
+    <t>수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LLM API 사용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 화면 우측 하단 플로팅 버튼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용자는 어려운 금융 용어 또는 금융상품 관련 질문을 입력하고 LLM 챗봇을 통해 쉬운 설명과 예시를 받을 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LLM을 활용한 금융용어 설명, 금융상품 쉬운 설명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1254,6 +1262,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1264,9 +1275,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1602,16 +1610,16 @@
         <v>19</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>197</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>198</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>16</v>
@@ -1622,22 +1630,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>202</v>
-      </c>
       <c r="G2" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -1648,19 +1656,19 @@
         <v>29</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>339</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -1668,22 +1676,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>202</v>
-      </c>
       <c r="G4" s="5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -1691,22 +1699,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>344</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -1714,19 +1722,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>205</v>
-      </c>
       <c r="D6" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E6" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>59</v>
@@ -1740,19 +1748,19 @@
         <v>42</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>202</v>
-      </c>
       <c r="G7" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -1760,22 +1768,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>350</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -1783,22 +1791,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E9" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>202</v>
-      </c>
       <c r="G9" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -1806,22 +1814,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>355</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -1832,19 +1840,19 @@
         <v>36</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>213</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -1855,19 +1863,19 @@
         <v>132</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D12" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>359</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -1875,19 +1883,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>219</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>220</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>117</v>
       </c>
       <c r="E13" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>209</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>210</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>118</v>
@@ -1896,7 +1904,7 @@
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>20</v>
@@ -1905,28 +1913,28 @@
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -1958,73 +1966,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
     </row>
     <row r="2" spans="1:15" ht="19.2" x14ac:dyDescent="0.4">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10" t="s">
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="38.4" x14ac:dyDescent="0.4">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
       <c r="J3" s="6" t="s">
         <v>13</v>
       </c>
@@ -2035,24 +2043,24 @@
         <v>15</v>
       </c>
       <c r="M3" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="N3" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="N3" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="O3" s="10"/>
+      <c r="O3" s="11"/>
     </row>
     <row r="4" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="8" t="s">
         <v>44</v>
       </c>
       <c r="E4" s="5" t="s">
@@ -2062,14 +2070,14 @@
         <v>44</v>
       </c>
       <c r="G4" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>224</v>
-      </c>
       <c r="J4" s="3" t="s">
         <v>45</v>
       </c>
@@ -2086,16 +2094,16 @@
         <v>45</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
       <c r="E5" s="5" t="s">
         <v>46</v>
       </c>
@@ -2103,13 +2111,13 @@
         <v>47</v>
       </c>
       <c r="G5" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>225</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>226</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>45</v>
@@ -2125,30 +2133,30 @@
         <v>45</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
         <v>3</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
       <c r="E6" s="5" t="s">
         <v>48</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="H6" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>228</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>229</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>45</v>
@@ -2162,20 +2170,20 @@
         <v>45</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="8" t="s">
         <v>51</v>
       </c>
       <c r="E7" s="5" t="s">
@@ -2185,14 +2193,14 @@
         <v>51</v>
       </c>
       <c r="G7" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>231</v>
-      </c>
       <c r="J7" s="3" t="s">
         <v>45</v>
       </c>
@@ -2209,16 +2217,16 @@
         <v>45</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="3">
         <v>5</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
       <c r="E8" s="5" t="s">
         <v>53</v>
       </c>
@@ -2226,14 +2234,14 @@
         <v>54</v>
       </c>
       <c r="G8" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I8" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>233</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>45</v>
       </c>
@@ -2250,7 +2258,7 @@
         <v>45</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
@@ -2260,8 +2268,8 @@
       <c r="B9" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
       <c r="E9" s="5" t="s">
         <v>56</v>
       </c>
@@ -2294,13 +2302,13 @@
       <c r="A10" s="3">
         <v>7</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="8" t="s">
         <v>29</v>
       </c>
       <c r="E10" s="5" t="s">
@@ -2310,13 +2318,13 @@
         <v>63</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>45</v>
@@ -2339,9 +2347,9 @@
       <c r="A11" s="3">
         <v>8</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
       <c r="E11" s="5" t="s">
         <v>65</v>
       </c>
@@ -2349,13 +2357,13 @@
         <v>66</v>
       </c>
       <c r="G11" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>300</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>301</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>45</v>
@@ -2378,14 +2386,14 @@
       <c r="A12" s="3">
         <v>9</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>203</v>
+      <c r="D12" s="8" t="s">
+        <v>202</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>70</v>
@@ -2397,78 +2405,78 @@
         <v>72</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I12" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O12" s="5" t="s">
         <v>278</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="O12" s="5" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="3">
         <v>10</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
       <c r="E13" s="5" t="s">
         <v>73</v>
       </c>
       <c r="F13" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="H13" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I13" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I13" s="5" t="s">
+      <c r="J13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O13" s="5" t="s">
         <v>282</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="O13" s="5" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="3">
         <v>11</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
       <c r="E14" s="5" t="s">
         <v>74</v>
       </c>
@@ -2503,14 +2511,14 @@
       <c r="A15" s="3">
         <v>12</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="12" t="s">
-        <v>321</v>
+      <c r="D15" s="8" t="s">
+        <v>320</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>80</v>
@@ -2519,13 +2527,13 @@
         <v>81</v>
       </c>
       <c r="G15" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I15" s="5" t="s">
         <v>302</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>303</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>45</v>
@@ -2550,9 +2558,9 @@
       <c r="A16" s="3">
         <v>13</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
       <c r="E16" s="5" t="s">
         <v>83</v>
       </c>
@@ -2587,9 +2595,9 @@
       <c r="A17" s="3">
         <v>14</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
       <c r="E17" s="5" t="s">
         <v>86</v>
       </c>
@@ -2624,56 +2632,56 @@
       <c r="A18" s="3">
         <v>15</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D18" s="12" t="s">
-        <v>284</v>
+      <c r="D18" s="8" t="s">
+        <v>283</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>92</v>
       </c>
       <c r="F18" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="H18" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O18" s="5" t="s">
         <v>286</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="O18" s="5" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3">
         <v>16</v>
       </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
       <c r="E19" s="5" t="s">
         <v>93</v>
       </c>
@@ -2681,13 +2689,13 @@
         <v>94</v>
       </c>
       <c r="G19" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I19" s="5" t="s">
         <v>288</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>289</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>45</v>
@@ -2710,30 +2718,30 @@
       <c r="A20" s="3">
         <v>17</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="12" t="s">
-        <v>290</v>
+      <c r="D20" s="8" t="s">
+        <v>289</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>98</v>
       </c>
       <c r="F20" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="H20" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I20" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>307</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>45</v>
       </c>
@@ -2750,71 +2758,71 @@
         <v>45</v>
       </c>
       <c r="O20" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3">
         <v>18</v>
       </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
       <c r="E21" s="5" t="s">
         <v>99</v>
       </c>
       <c r="F21" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="H21" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I21" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I21" s="5" t="s">
+      <c r="J21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O21" s="5" t="s">
         <v>310</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="O21" s="5" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="3">
         <v>19</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
       <c r="E22" s="5" t="s">
         <v>100</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G22" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I22" s="5" t="s">
         <v>312</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>313</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>45</v>
@@ -2830,36 +2838,36 @@
         <v>45</v>
       </c>
       <c r="O22" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="3">
         <v>20</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="D23" s="12" t="s">
-        <v>221</v>
+      <c r="D23" s="8" t="s">
+        <v>220</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>103</v>
       </c>
       <c r="F23" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="H23" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I23" s="5" t="s">
         <v>236</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>237</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>45</v>
@@ -2875,31 +2883,31 @@
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="3">
         <v>21</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
       <c r="E24" s="5" t="s">
         <v>104</v>
       </c>
       <c r="F24" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="H24" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I24" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>240</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>45</v>
       </c>
@@ -2916,31 +2924,31 @@
         <v>45</v>
       </c>
       <c r="O24" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="3">
         <v>22</v>
       </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
       <c r="E25" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F25" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="G25" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="H25" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I25" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>244</v>
-      </c>
       <c r="J25" s="3" t="s">
         <v>45</v>
       </c>
@@ -2957,37 +2965,37 @@
         <v>45</v>
       </c>
       <c r="O25" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="3">
         <v>23</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="D26" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="E26" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="F26" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="G26" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="H26" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I26" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>251</v>
-      </c>
       <c r="J26" s="3" t="s">
         <v>45</v>
       </c>
@@ -3004,30 +3012,30 @@
         <v>45</v>
       </c>
       <c r="O26" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="3">
         <v>24</v>
       </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
       <c r="E27" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="H27" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I27" s="5" t="s">
         <v>293</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>294</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>45</v>
@@ -3043,20 +3051,20 @@
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="3">
         <v>25</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="8" t="s">
         <v>107</v>
       </c>
       <c r="E28" s="5" t="s">
@@ -3066,13 +3074,13 @@
         <v>109</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>45</v>
@@ -3097,9 +3105,9 @@
       <c r="A29" s="3">
         <v>26</v>
       </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
       <c r="E29" s="5" t="s">
         <v>111</v>
       </c>
@@ -3110,10 +3118,10 @@
         <v>113</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>45</v>
@@ -3138,17 +3146,17 @@
       <c r="A30" s="3">
         <v>27</v>
       </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
       <c r="E30" s="5" t="s">
         <v>115</v>
       </c>
       <c r="F30" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="G30" s="5" t="s">
         <v>255</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>256</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="5"/>
@@ -3168,18 +3176,18 @@
         <v>45</v>
       </c>
       <c r="O30" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3">
         <v>28</v>
       </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
       <c r="E31" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>116</v>
@@ -3203,20 +3211,20 @@
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="3">
         <v>29</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="8" t="s">
         <v>121</v>
       </c>
       <c r="E32" s="5" t="s">
@@ -3253,9 +3261,9 @@
       <c r="A33" s="3">
         <v>30</v>
       </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
       <c r="E33" s="5" t="s">
         <v>126</v>
       </c>
@@ -3290,14 +3298,14 @@
       <c r="A34" s="3">
         <v>31</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="D34" s="12" t="s">
-        <v>320</v>
+      <c r="D34" s="8" t="s">
+        <v>319</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>133</v>
@@ -3333,9 +3341,9 @@
       <c r="A35" s="3">
         <v>32</v>
       </c>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
       <c r="E35" s="5" t="s">
         <v>137</v>
       </c>
@@ -3345,8 +3353,12 @@
       <c r="G35" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="H35" s="3"/>
-      <c r="I35" s="5"/>
+      <c r="H35" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>358</v>
+      </c>
       <c r="J35" s="3" t="s">
         <v>45</v>
       </c>
@@ -3362,25 +3374,23 @@
       <c r="N35" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="O35" s="5" t="s">
-        <v>140</v>
-      </c>
+      <c r="O35" s="5"/>
     </row>
     <row r="36" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="3">
         <v>33</v>
       </c>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
       <c r="E36" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F36" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="G36" s="5" t="s">
         <v>142</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>143</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="5"/>
@@ -3400,71 +3410,71 @@
         <v>45</v>
       </c>
       <c r="O36" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3">
         <v>34</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C37" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="D37" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="E37" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="D37" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="E37" s="5" t="s">
+      <c r="F37" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="G37" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="H37" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O37" s="5" t="s">
         <v>149</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="N37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="O37" s="5" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="3">
         <v>35</v>
       </c>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
       <c r="E38" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F38" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="G38" s="5" t="s">
         <v>152</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>153</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="5"/>
@@ -3484,7 +3494,7 @@
         <v>45</v>
       </c>
       <c r="O38" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
@@ -3492,29 +3502,29 @@
         <v>36</v>
       </c>
       <c r="B39" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="D39" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="E39" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="E39" s="5" t="s">
+      <c r="F39" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="F39" s="5" t="s">
-        <v>158</v>
-      </c>
       <c r="G39" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I39" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="H39" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I39" s="5" t="s">
-        <v>259</v>
-      </c>
       <c r="J39" s="3" t="s">
         <v>45</v>
       </c>
@@ -3531,30 +3541,30 @@
         <v>45</v>
       </c>
       <c r="O39" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="3">
         <v>37</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C40" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="D40" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="F40" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="D40" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="E40" s="5" t="s">
+      <c r="G40" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>163</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="5"/>
@@ -3581,17 +3591,17 @@
       <c r="A41" s="3">
         <v>38</v>
       </c>
-      <c r="B41" s="12"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
       <c r="E41" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F41" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="G41" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>166</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="5"/>
@@ -3611,24 +3621,24 @@
         <v>45</v>
       </c>
       <c r="O41" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="3">
         <v>39</v>
       </c>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
       <c r="E42" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="F42" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="G42" s="5" t="s">
         <v>169</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>170</v>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="5"/>
@@ -3648,36 +3658,36 @@
         <v>45</v>
       </c>
       <c r="O42" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="3">
         <v>40</v>
       </c>
-      <c r="B43" s="12" t="s">
+      <c r="B43" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="E43" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C43" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="D43" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="E43" s="5" t="s">
+      <c r="F43" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="G43" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="G43" s="5" t="s">
-        <v>174</v>
-      </c>
       <c r="H43" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>45</v>
@@ -3702,17 +3712,17 @@
       <c r="A44" s="3">
         <v>41</v>
       </c>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
       <c r="E44" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F44" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="G44" s="5" t="s">
         <v>260</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>261</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="5"/>
@@ -3732,30 +3742,30 @@
         <v>45</v>
       </c>
       <c r="O44" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="3">
         <v>42</v>
       </c>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
       <c r="E45" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F45" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="G45" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="G45" s="5" t="s">
-        <v>177</v>
-      </c>
       <c r="H45" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>45</v>
@@ -3773,36 +3783,36 @@
         <v>45</v>
       </c>
       <c r="O45" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="3">
         <v>43</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C46" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="D46" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E46" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D46" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E46" s="5" t="s">
+      <c r="F46" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="F46" s="5" t="s">
-        <v>181</v>
-      </c>
       <c r="G46" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I46" s="5" t="s">
         <v>273</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I46" s="5" t="s">
-        <v>274</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>45</v>
@@ -3827,17 +3837,17 @@
       <c r="A47" s="3">
         <v>44</v>
       </c>
-      <c r="B47" s="12"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
       <c r="E47" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="F47" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="F47" s="5" t="s">
+      <c r="G47" s="5" t="s">
         <v>183</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>184</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="5"/>
@@ -3857,30 +3867,30 @@
         <v>45</v>
       </c>
       <c r="O47" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="3">
         <v>45</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C48" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="C48" s="12" t="s">
+      <c r="D48" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="E48" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="E48" s="5" t="s">
+      <c r="F48" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="F48" s="5" t="s">
+      <c r="G48" s="5" t="s">
         <v>189</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>190</v>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="5"/>
@@ -3900,24 +3910,24 @@
         <v>45</v>
       </c>
       <c r="O48" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3">
         <v>46</v>
       </c>
-      <c r="B49" s="12"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
       <c r="E49" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F49" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="F49" s="5" t="s">
+      <c r="G49" s="5" t="s">
         <v>193</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>194</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="5"/>
@@ -3940,27 +3950,32 @@
     </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="D23:D25"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="D34:D36"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="D28:D31"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="D40:D42"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="J2:N2"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B28:B31"/>
     <mergeCell ref="B46:B47"/>
     <mergeCell ref="B48:B49"/>
     <mergeCell ref="C4:C6"/>
@@ -3977,32 +3992,27 @@
     <mergeCell ref="C34:C36"/>
     <mergeCell ref="C37:C38"/>
     <mergeCell ref="B32:B33"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="J2:N2"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="D40:D42"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="D34:D36"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="D28:D31"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="D12:D14"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4061,7 +4071,7 @@
         <v>27</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -4072,7 +4082,7 @@
         <v>29</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -4080,10 +4090,10 @@
         <v>30</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.4">
@@ -4091,10 +4101,10 @@
         <v>31</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -4102,10 +4112,10 @@
         <v>32</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -4116,7 +4126,7 @@
         <v>34</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -4127,7 +4137,7 @@
         <v>36</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -4138,7 +4148,7 @@
         <v>132</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>327</v>
+        <v>361</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -4160,7 +4170,7 @@
         <v>42</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
@@ -4168,55 +4178,55 @@
         <v>19</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="52.2" x14ac:dyDescent="0.4">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A16" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="52.2" x14ac:dyDescent="0.4">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A17" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="52.2" x14ac:dyDescent="0.4">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A18" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>43</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
